--- a/thesis-final/arabic/WSN_Protocol_Comparison_AR.xlsx
+++ b/thesis-final/arabic/WSN_Protocol_Comparison_AR.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="310">
   <si>
     <t xml:space="preserve">ملف مقارنة بروتوكولات الـ Clustering في شبكات الحساسات</t>
   </si>
@@ -249,6 +249,42 @@
   </si>
   <si>
     <t xml:space="preserve">El-Sayed, Abd-Elgaber and Refaay, “An Intelligent RL Enhanced Improved LEACH Protocol for Prolonging WSN Lifetime,” Scientific Reports, 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J. Jassbi and S. Moridi, “Fault Tolerance and Energy Efficient Clustering Algorithm in Wireless Sensor Networks: FTEC,” Wireless Personal Communications, 2019. doi:10.1007/s11277-019-06281-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R. Pachlor, D. Shrimankar, K. K. Nagwanshi and M. Paliwal, “Cluster-Head Rotation Approaches in Sensor Networks: A Review,” arXiv:2206.08892, 2022.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. Li, M. Ye, G. Chen and J. Wu, “An Energy-Efficient Unequal Clustering Mechanism for Wireless Sensor Networks,” Proc. IEEE MASS, 2005.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V. Chauhan and S. Soni, “Energy Aware Unequal Clustering Algorithm with Multi-hop Routing via Low Degree Relay Nodes for Wireless Sensor Networks,” J. Ambient Intelligence and Humanized Computing, vol. 12, pp. 2469–2482, 2021. doi:10.1007/s12652-020-02385-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W. B. Heinzelman, A. P. Chandrakasan and H. Balakrishnan, “An Application-Specific Protocol Architecture for Wireless Microsensor Networks,” IEEE Trans. Wireless Communications, 2002.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ns-3 Network Simulator, release 3.41, https://www.nsnam.org</t>
   </si>
   <si>
     <t xml:space="preserve">لوحة الملخص — أحسن نسخة من كل عيلة (الـ BS في النص)</t>
@@ -1823,11 +1859,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="69346111"/>
-        <c:axId val="88085423"/>
+        <c:axId val="52855859"/>
+        <c:axId val="76906376"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="69346111"/>
+        <c:axId val="52855859"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1859,7 +1895,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88085423"/>
+        <c:crossAx val="76906376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1867,7 +1903,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88085423"/>
+        <c:axId val="76906376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1909,7 +1945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69346111"/>
+        <c:crossAx val="52855859"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2133,11 +2169,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="40002719"/>
-        <c:axId val="65135457"/>
+        <c:axId val="19659403"/>
+        <c:axId val="33074163"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40002719"/>
+        <c:axId val="19659403"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2169,7 +2205,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65135457"/>
+        <c:crossAx val="33074163"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2177,7 +2213,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65135457"/>
+        <c:axId val="33074163"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2221,7 +2257,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40002719"/>
+        <c:crossAx val="19659403"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2769,11 +2805,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="30100152"/>
-        <c:axId val="54698122"/>
+        <c:axId val="29995486"/>
+        <c:axId val="4271713"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30100152"/>
+        <c:axId val="29995486"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2805,7 +2841,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54698122"/>
+        <c:crossAx val="4271713"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2813,7 +2849,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54698122"/>
+        <c:axId val="4271713"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2889,7 +2925,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30100152"/>
+        <c:crossAx val="29995486"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3282,11 +3318,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="69728792"/>
-        <c:axId val="74835865"/>
+        <c:axId val="84339763"/>
+        <c:axId val="98573180"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="69728792"/>
+        <c:axId val="84339763"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3318,7 +3354,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74835865"/>
+        <c:crossAx val="98573180"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3326,7 +3362,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74835865"/>
+        <c:axId val="98573180"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3402,7 +3438,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69728792"/>
+        <c:crossAx val="84339763"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3769,7 +3805,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -4085,6 +4121,54 @@
       </c>
       <c r="B44" s="5" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -4113,40 +4197,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C5" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A5)*('المقارنة الموحدة'!$C$5:$C$28=B5),0),0))</f>
@@ -4167,10 +4251,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C6" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A6)*('المقارنة الموحدة'!$C$5:$C$28=B6),0),0))</f>
@@ -4191,10 +4275,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C7" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A7)*('المقارنة الموحدة'!$C$5:$C$28=B7),0),0))</f>
@@ -4215,10 +4299,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A8)*('المقارنة الموحدة'!$C$5:$C$28=B8),0),0))</f>
@@ -4239,10 +4323,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A9)*('المقارنة الموحدة'!$C$5:$C$28=B9),0),0))</f>
@@ -4263,10 +4347,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C10" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A10)*('المقارنة الموحدة'!$C$5:$C$28=B10),0),0))</f>
@@ -4287,10 +4371,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A11)*('المقارنة الموحدة'!$C$5:$C$28=B11),0),0))</f>
@@ -4311,10 +4395,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A12)*('المقارنة الموحدة'!$C$5:$C$28=B12),0),0))</f>
@@ -4335,10 +4419,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C13" s="15" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A13)*('المقارنة الموحدة'!$C$5:$C$28=B13),0),0))</f>
@@ -4359,12 +4443,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">C13/C9-1</f>
@@ -4373,7 +4457,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">C13/C5-1</f>
@@ -4382,7 +4466,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C18" s="20" t="n">
         <f aca="false">(F13-F11)*100</f>
@@ -4391,7 +4475,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C19" s="19" t="n">
         <f aca="false">'نص مقابل بعيد'!F9/'نص مقابل بعيد'!F7-1</f>
@@ -4400,7 +4484,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4429,188 +4513,188 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -4644,64 +4728,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>1409</v>
@@ -4734,16 +4818,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>323</v>
@@ -4776,16 +4860,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>338</v>
@@ -4818,16 +4902,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>1324</v>
@@ -4860,16 +4944,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>1440</v>
@@ -4902,16 +4986,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>1247</v>
@@ -4944,16 +5028,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>2177</v>
@@ -4986,16 +5070,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>2347</v>
@@ -5028,16 +5112,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>1653</v>
@@ -5070,16 +5154,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>2502</v>
@@ -5112,16 +5196,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>330</v>
@@ -5154,16 +5238,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>345</v>
@@ -5196,16 +5280,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>1730</v>
@@ -5238,16 +5322,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>1513</v>
@@ -5280,16 +5364,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>1513</v>
@@ -5322,16 +5406,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>1730</v>
@@ -5364,16 +5448,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>1621</v>
@@ -5406,16 +5490,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>1551</v>
@@ -5448,16 +5532,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>1551</v>
@@ -5490,16 +5574,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>1491</v>
@@ -5532,16 +5616,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="E25" s="9" t="n">
         <v>1381</v>
@@ -5574,16 +5658,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>1730</v>
@@ -5616,16 +5700,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E27" s="15" t="n">
         <v>2621</v>
@@ -5658,16 +5742,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E28" s="15" t="n">
         <v>2621</v>
@@ -5700,12 +5784,12 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -5738,64 +5822,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>932</v>
@@ -5836,21 +5920,21 @@
         <v>0.485238455715367</v>
       </c>
       <c r="N5" s="22" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="O5" s="22" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>1106</v>
@@ -5885,15 +5969,15 @@
         <v>-0.317635270541082</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>1578</v>
@@ -5934,21 +6018,21 @@
         <v>0.332256575911398</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>493</v>
@@ -5983,18 +6067,18 @@
         <v>0.81447963800905</v>
       </c>
       <c r="N8" s="23" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>4312</v>
@@ -6032,15 +6116,15 @@
         <v>0.90495867768595</v>
       </c>
       <c r="N9" s="22" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>1250</v>
@@ -6081,20 +6165,20 @@
         <v>0.934455270150576</v>
       </c>
       <c r="N10" s="23" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -6128,64 +6212,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>330</v>
@@ -6200,13 +6284,13 @@
         <v>0.9974</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="L5" s="25" t="n">
         <f aca="false">G5/$G$5-1</f>
@@ -6215,16 +6299,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C6" s="30" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>345</v>
@@ -6257,16 +6341,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>5</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>1730</v>
@@ -6299,16 +6383,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C8" s="30" t="n">
         <v>15</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>1513</v>
@@ -6341,16 +6425,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>15</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>1513</v>
@@ -6383,16 +6467,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C10" s="30" t="n">
         <v>5</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>1730</v>
@@ -6425,16 +6509,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>10</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>1621</v>
@@ -6467,16 +6551,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C12" s="30" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1551</v>
@@ -6509,16 +6593,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C13" s="27" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>1551</v>
@@ -6551,16 +6635,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C14" s="30" t="n">
         <v>5</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>1266</v>
@@ -6593,16 +6677,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>1266</v>
@@ -6635,16 +6719,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C16" s="30" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>1491</v>
@@ -6677,16 +6761,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C17" s="27" t="n">
         <v>10</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>1381</v>
@@ -6719,16 +6803,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C18" s="30" t="n">
         <v>5</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>1730</v>
@@ -6761,16 +6845,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C19" s="35" t="n">
         <v>5</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E19" s="15" t="n">
         <v>2621</v>
@@ -6803,16 +6887,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C20" s="35" t="n">
         <v>5</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>1471</v>
@@ -6845,16 +6929,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C21" s="35" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E21" s="15" t="n">
         <v>2621</v>
@@ -6887,16 +6971,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C22" s="35" t="n">
         <v>5</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="E22" s="15" t="n">
         <v>1716</v>
@@ -6929,29 +7013,29 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="43" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="44" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7289,55 +7373,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>1730</v>
@@ -7378,7 +7462,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>1551</v>
@@ -7419,7 +7503,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>1551</v>
@@ -7460,7 +7544,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>2621</v>
@@ -7501,7 +7585,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>2621</v>
@@ -7542,7 +7626,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -7576,54 +7660,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>2621</v>
@@ -7651,10 +7735,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>2621</v>
@@ -7682,10 +7766,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>2585</v>
@@ -7713,10 +7797,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>2621</v>
@@ -7744,10 +7828,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>1821</v>
@@ -7775,10 +7859,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>2171</v>
@@ -7806,10 +7890,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>1730</v>
@@ -7837,47 +7921,47 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>2621</v>
@@ -7906,10 +7990,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>2566</v>
@@ -7938,10 +8022,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C19" s="15" t="n">
         <v>2621</v>
@@ -7970,10 +8054,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>1471</v>
@@ -8002,10 +8086,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>1696</v>
@@ -8034,10 +8118,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>1716</v>
@@ -8066,35 +8150,35 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>1688</v>
@@ -8111,10 +8195,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>2618</v>
@@ -8131,10 +8215,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>1152</v>
@@ -8151,10 +8235,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C30" s="15" t="n">
         <v>1487</v>
@@ -8171,12 +8255,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/thesis-final/arabic/WSN_Protocol_Comparison_AR.xlsx
+++ b/thesis-final/arabic/WSN_Protocol_Comparison_AR.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="311">
   <si>
     <t xml:space="preserve">ملف مقارنة بروتوكولات الـ Clustering في شبكات الحساسات</t>
   </si>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">FND بتاع v8-Chain لما الـ BS بعيد مقارنة بـ v7 بعيد</t>
   </si>
   <si>
-    <t xml:space="preserve">ملاحظة مهمة: HEED وSH-LEACH المحسّن عندهم PDR أعلى شوية من v8-Chain، بس أول نود فيهم بيموت بدري جدًا. وPEGASIS عنده LND أعلى، بس أول نود فيه بيموت قبلنا بحوالي 1300 round.</t>
+    <t xml:space="preserve">ملاحظة مهمة: LEACH وPEGASIS وHEED وSH-LEACH المحسّن عندهم PDR أعلى شوية من v8-Chain (99.40–99.79%)، بس أول نود فيهم بتموت قبلنا بـ 1,200 لـ 2,000 round. وPEGASIS عنده LND أعلى (3504)، بس أول نود فيه بتموت قبلنا بحوالي 1300 round.</t>
   </si>
   <si>
     <t xml:space="preserve">شرح المصطلحات بالعربي البسيط</t>
@@ -698,22 +698,25 @@
     <t xml:space="preserve">مصدر الرقم المنشور</t>
   </si>
   <si>
+    <t xml:space="preserve">50×50 م، BS بعيد، معادلة راديو واحدة، من غير طاقة الـ setup (زي البحث)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heinzelman وآخرين، 2000 — جدول 2 (0.5 جول)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مش موجود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رسم بس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500 نود، الـ Sink عند (50,175)، طاقة 2 جول، رسالة 125 بايت، 5 frames في الـ round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Younis و Fahmy، 2004 — رسم بياني بس (Fig. 8)</t>
+  </si>
+  <si>
     <t xml:space="preserve">50×50 م، BS بعيد، معادلة راديو واحدة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heinzelman وآخرين، 2000 — جدول 2 (0.5 جول)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مش موجود</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رسم بس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إعدادات جدول 2، BS بعيد، طاقة 2 جول، رسالة 800 بت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Younis و Fahmy، 2004 — رسم بياني بس (Fig. 8)</t>
   </si>
   <si>
     <t xml:space="preserve">Lindsey و Raghavendra، 2002 — جدول 1 (50×50 م)</t>
@@ -1583,10 +1586,10 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>1409</c:v>
+                  <c:v>1383</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>323</c:v>
+                  <c:v>634</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1324</c:v>
@@ -1705,13 +1708,13 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>1626</c:v>
+                  <c:v>1586</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>570</c:v>
+                  <c:v>1216</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2353</c:v>
+                  <c:v>2352</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1600</c:v>
@@ -1827,13 +1830,13 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>1962</c:v>
+                  <c:v>1842</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1362</c:v>
+                  <c:v>1883</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2887</c:v>
+                  <c:v>3504</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1649</c:v>
@@ -1859,11 +1862,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="52855859"/>
-        <c:axId val="76906376"/>
+        <c:axId val="96485175"/>
+        <c:axId val="28098681"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52855859"/>
+        <c:axId val="96485175"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1895,7 +1898,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76906376"/>
+        <c:crossAx val="28098681"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1903,7 +1906,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76906376"/>
+        <c:axId val="28098681"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1945,7 +1948,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52855859"/>
+        <c:crossAx val="96485175"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2137,13 +2140,13 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.9837</c:v>
+                  <c:v>0.994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9969</c:v>
+                  <c:v>0.9968</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9867</c:v>
+                  <c:v>0.9942</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.9979</c:v>
@@ -2169,11 +2172,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="19659403"/>
-        <c:axId val="33074163"/>
+        <c:axId val="93267099"/>
+        <c:axId val="22553498"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19659403"/>
+        <c:axId val="93267099"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2205,7 +2208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33074163"/>
+        <c:crossAx val="22553498"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2213,7 +2216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33074163"/>
+        <c:axId val="22553498"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2257,7 +2260,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19659403"/>
+        <c:crossAx val="93267099"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2805,11 +2808,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="29995486"/>
-        <c:axId val="4271713"/>
+        <c:axId val="96224763"/>
+        <c:axId val="67249896"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="29995486"/>
+        <c:axId val="96224763"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2841,7 +2844,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4271713"/>
+        <c:crossAx val="67249896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2849,7 +2852,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4271713"/>
+        <c:axId val="67249896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2925,7 +2928,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29995486"/>
+        <c:crossAx val="96224763"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3318,11 +3321,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="84339763"/>
-        <c:axId val="98573180"/>
+        <c:axId val="75480169"/>
+        <c:axId val="23161357"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84339763"/>
+        <c:axId val="75480169"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3354,7 +3357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98573180"/>
+        <c:crossAx val="23161357"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3362,7 +3365,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="98573180"/>
+        <c:axId val="23161357"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3438,7 +3441,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84339763"/>
+        <c:crossAx val="75480169"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4234,19 +4237,19 @@
       </c>
       <c r="C5" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A5)*('المقارنة الموحدة'!$C$5:$C$28=B5),0),0))</f>
-        <v>1409</v>
+        <v>1383</v>
       </c>
       <c r="D5" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$F$5:$F$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A5)*('المقارنة الموحدة'!$C$5:$C$28=B5),0),0))</f>
-        <v>1626</v>
+        <v>1586</v>
       </c>
       <c r="E5" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$G$5:$G$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A5)*('المقارنة الموحدة'!$C$5:$C$28=B5),0),0))</f>
-        <v>1962</v>
+        <v>1842</v>
       </c>
       <c r="F5" s="10" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$H$5:$H$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A5)*('المقارنة الموحدة'!$C$5:$C$28=B5),0),0))</f>
-        <v>0.9837</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4258,19 +4261,19 @@
       </c>
       <c r="C6" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A6)*('المقارنة الموحدة'!$C$5:$C$28=B6),0),0))</f>
-        <v>323</v>
+        <v>634</v>
       </c>
       <c r="D6" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$F$5:$F$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A6)*('المقارنة الموحدة'!$C$5:$C$28=B6),0),0))</f>
-        <v>570</v>
+        <v>1216</v>
       </c>
       <c r="E6" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$G$5:$G$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A6)*('المقارنة الموحدة'!$C$5:$C$28=B6),0),0))</f>
-        <v>1362</v>
+        <v>1883</v>
       </c>
       <c r="F6" s="13" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$H$5:$H$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A6)*('المقارنة الموحدة'!$C$5:$C$28=B6),0),0))</f>
-        <v>0.9969</v>
+        <v>0.9968</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4286,15 +4289,15 @@
       </c>
       <c r="D7" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$F$5:$F$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A7)*('المقارنة الموحدة'!$C$5:$C$28=B7),0),0))</f>
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$G$5:$G$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A7)*('المقارنة الموحدة'!$C$5:$C$28=B7),0),0))</f>
-        <v>2887</v>
+        <v>3504</v>
       </c>
       <c r="F7" s="10" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$H$5:$H$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A7)*('المقارنة الموحدة'!$C$5:$C$28=B7),0),0))</f>
-        <v>0.9867</v>
+        <v>0.9942</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4461,7 +4464,7 @@
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">C13/C5-1</f>
-        <v>0.860184528034067</v>
+        <v>0.895155459146782</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4788,16 +4791,16 @@
         <v>167</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>1409</v>
+        <v>1383</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>1626</v>
+        <v>1586</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>1962</v>
+        <v>1842</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.9837</v>
+        <v>0.994</v>
       </c>
       <c r="I5" s="25" t="n">
         <f aca="false">G5/$G$5-1</f>
@@ -4805,15 +4808,15 @@
       </c>
       <c r="J5" s="26" t="n">
         <f aca="false">E5/G5</f>
-        <v>0.718144750254842</v>
+        <v>0.750814332247557</v>
       </c>
       <c r="K5" s="27" t="n">
         <f aca="false">RANK(G5,$G$5:$G$28)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L5" s="27" t="n">
         <f aca="false">RANK(H5,$H$5:$H$28)</f>
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4830,32 +4833,32 @@
         <v>168</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>323</v>
+        <v>634</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>570</v>
+        <v>1216</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1362</v>
+        <v>1883</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.9969</v>
+        <v>0.9968</v>
       </c>
       <c r="I6" s="28" t="n">
         <f aca="false">G6/$G$5-1</f>
-        <v>-0.305810397553517</v>
+        <v>0.0222584147665581</v>
       </c>
       <c r="J6" s="29" t="n">
         <f aca="false">E6/G6</f>
-        <v>0.237151248164464</v>
+        <v>0.336696760488582</v>
       </c>
       <c r="K6" s="30" t="n">
         <f aca="false">RANK(G6,$G$5:$G$28)</f>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L6" s="30" t="n">
         <f aca="false">RANK(H6,$H$5:$H$28)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4872,32 +4875,32 @@
         <v>171</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>338</v>
+        <v>743</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>549</v>
+        <v>1154</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>1502</v>
+        <v>1960</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.9967</v>
+        <v>0.9974</v>
       </c>
       <c r="I7" s="25" t="n">
         <f aca="false">G7/$G$5-1</f>
-        <v>-0.234454638124363</v>
+        <v>0.0640608034744843</v>
       </c>
       <c r="J7" s="26" t="n">
         <f aca="false">E7/G7</f>
-        <v>0.225033288948069</v>
+        <v>0.379081632653061</v>
       </c>
       <c r="K7" s="27" t="n">
         <f aca="false">RANK(G7,$G$5:$G$28)</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L7" s="27" t="n">
         <f aca="false">RANK(H7,$H$5:$H$28)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4917,29 +4920,29 @@
         <v>1324</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2887</v>
+        <v>3504</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.9867</v>
+        <v>0.9942</v>
       </c>
       <c r="I8" s="28" t="n">
         <f aca="false">G8/$G$5-1</f>
-        <v>0.471457696228338</v>
+        <v>0.90228013029316</v>
       </c>
       <c r="J8" s="29" t="n">
         <f aca="false">E8/G8</f>
-        <v>0.458607551091098</v>
+        <v>0.377853881278539</v>
       </c>
       <c r="K8" s="30" t="n">
         <f aca="false">RANK(G8,$G$5:$G$28)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" s="30" t="n">
         <f aca="false">RANK(H8,$H$5:$H$28)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4969,7 +4972,7 @@
       </c>
       <c r="I9" s="25" t="n">
         <f aca="false">G9/$G$5-1</f>
-        <v>-0.182466870540265</v>
+        <v>-0.129207383279044</v>
       </c>
       <c r="J9" s="26" t="n">
         <f aca="false">E9/G9</f>
@@ -4977,11 +4980,11 @@
       </c>
       <c r="K9" s="27" t="n">
         <f aca="false">RANK(G9,$G$5:$G$28)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L9" s="27" t="n">
         <f aca="false">RANK(H9,$H$5:$H$28)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5011,7 +5014,7 @@
       </c>
       <c r="I10" s="28" t="n">
         <f aca="false">G10/$G$5-1</f>
-        <v>-0.159531090723751</v>
+        <v>-0.104777415852334</v>
       </c>
       <c r="J10" s="29" t="n">
         <f aca="false">E10/G10</f>
@@ -5019,7 +5022,7 @@
       </c>
       <c r="K10" s="30" t="n">
         <f aca="false">RANK(G10,$G$5:$G$28)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L10" s="30" t="n">
         <f aca="false">RANK(H10,$H$5:$H$28)</f>
@@ -5053,7 +5056,7 @@
       </c>
       <c r="I11" s="25" t="n">
         <f aca="false">G11/$G$5-1</f>
-        <v>0.174821610601427</v>
+        <v>0.251357220412595</v>
       </c>
       <c r="J11" s="26" t="n">
         <f aca="false">E11/G11</f>
@@ -5095,7 +5098,7 @@
       </c>
       <c r="I12" s="28" t="n">
         <f aca="false">G12/$G$5-1</f>
-        <v>0.273700305810398</v>
+        <v>0.356677524429967</v>
       </c>
       <c r="J12" s="29" t="n">
         <f aca="false">E12/G12</f>
@@ -5137,7 +5140,7 @@
       </c>
       <c r="I13" s="25" t="n">
         <f aca="false">G13/$G$5-1</f>
-        <v>0.113149847094801</v>
+        <v>0.185667752442997</v>
       </c>
       <c r="J13" s="26" t="n">
         <f aca="false">E13/G13</f>
@@ -5179,7 +5182,7 @@
       </c>
       <c r="I14" s="28" t="n">
         <f aca="false">G14/$G$5-1</f>
-        <v>0.940876656472987</v>
+        <v>1.06731813246471</v>
       </c>
       <c r="J14" s="29" t="n">
         <f aca="false">E14/G14</f>
@@ -5221,7 +5224,7 @@
       </c>
       <c r="I15" s="25" t="n">
         <f aca="false">G15/$G$5-1</f>
-        <v>-0.328236493374108</v>
+        <v>-0.284473398479913</v>
       </c>
       <c r="J15" s="26" t="n">
         <f aca="false">E15/G15</f>
@@ -5263,7 +5266,7 @@
       </c>
       <c r="I16" s="28" t="n">
         <f aca="false">G16/$G$5-1</f>
-        <v>-0.290010193679918</v>
+        <v>-0.243756786102063</v>
       </c>
       <c r="J16" s="29" t="n">
         <f aca="false">E16/G16</f>
@@ -5271,7 +5274,7 @@
       </c>
       <c r="K16" s="30" t="n">
         <f aca="false">RANK(G16,$G$5:$G$28)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L16" s="30" t="n">
         <f aca="false">RANK(H16,$H$5:$H$28)</f>
@@ -5305,7 +5308,7 @@
       </c>
       <c r="I17" s="25" t="n">
         <f aca="false">G17/$G$5-1</f>
-        <v>0.377675840978593</v>
+        <v>0.46742671009772</v>
       </c>
       <c r="J17" s="26" t="n">
         <f aca="false">E17/G17</f>
@@ -5347,7 +5350,7 @@
       </c>
       <c r="I18" s="28" t="n">
         <f aca="false">G18/$G$5-1</f>
-        <v>0.284913353720693</v>
+        <v>0.368621064060803</v>
       </c>
       <c r="J18" s="29" t="n">
         <f aca="false">E18/G18</f>
@@ -5389,7 +5392,7 @@
       </c>
       <c r="I19" s="25" t="n">
         <f aca="false">G19/$G$5-1</f>
-        <v>0.231396534148828</v>
+        <v>0.311617806731813</v>
       </c>
       <c r="J19" s="26" t="n">
         <f aca="false">E19/G19</f>
@@ -5431,7 +5434,7 @@
       </c>
       <c r="I20" s="28" t="n">
         <f aca="false">G20/$G$5-1</f>
-        <v>0.0988786952089704</v>
+        <v>0.170466883821933</v>
       </c>
       <c r="J20" s="29" t="n">
         <f aca="false">E20/G20</f>
@@ -5473,7 +5476,7 @@
       </c>
       <c r="I21" s="25" t="n">
         <f aca="false">G21/$G$5-1</f>
-        <v>0.167686034658512</v>
+        <v>0.243756786102063</v>
       </c>
       <c r="J21" s="26" t="n">
         <f aca="false">E21/G21</f>
@@ -5515,7 +5518,7 @@
       </c>
       <c r="I22" s="28" t="n">
         <f aca="false">G22/$G$5-1</f>
-        <v>0.073394495412844</v>
+        <v>0.143322475570033</v>
       </c>
       <c r="J22" s="29" t="n">
         <f aca="false">E22/G22</f>
@@ -5557,7 +5560,7 @@
       </c>
       <c r="I23" s="25" t="n">
         <f aca="false">G23/$G$5-1</f>
-        <v>0.0530071355759429</v>
+        <v>0.121606948968513</v>
       </c>
       <c r="J23" s="26" t="n">
         <f aca="false">E23/G23</f>
@@ -5569,7 +5572,7 @@
       </c>
       <c r="L23" s="27" t="n">
         <f aca="false">RANK(H23,$H$5:$H$28)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5599,7 +5602,7 @@
       </c>
       <c r="I24" s="28" t="n">
         <f aca="false">G24/$G$5-1</f>
-        <v>0.0632008154943935</v>
+        <v>0.132464712269273</v>
       </c>
       <c r="J24" s="29" t="n">
         <f aca="false">E24/G24</f>
@@ -5611,7 +5614,7 @@
       </c>
       <c r="L24" s="30" t="n">
         <f aca="false">RANK(H24,$H$5:$H$28)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5641,7 +5644,7 @@
       </c>
       <c r="I25" s="25" t="n">
         <f aca="false">G25/$G$5-1</f>
-        <v>0.142201834862385</v>
+        <v>0.216612377850163</v>
       </c>
       <c r="J25" s="26" t="n">
         <f aca="false">E25/G25</f>
@@ -5683,7 +5686,7 @@
       </c>
       <c r="I26" s="28" t="n">
         <f aca="false">G26/$G$5-1</f>
-        <v>0.632517838939857</v>
+        <v>0.738870792616721</v>
       </c>
       <c r="J26" s="29" t="n">
         <f aca="false">E26/G26</f>
@@ -5691,7 +5694,7 @@
       </c>
       <c r="K26" s="30" t="n">
         <f aca="false">RANK(G26,$G$5:$G$28)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="30" t="n">
         <f aca="false">RANK(H26,$H$5:$H$28)</f>
@@ -5725,7 +5728,7 @@
       </c>
       <c r="I27" s="33" t="n">
         <f aca="false">G27/$G$5-1</f>
-        <v>0.4072375127421</v>
+        <v>0.498914223669924</v>
       </c>
       <c r="J27" s="34" t="n">
         <f aca="false">E27/G27</f>
@@ -5737,7 +5740,7 @@
       </c>
       <c r="L27" s="35" t="n">
         <f aca="false">RANK(H27,$H$5:$H$28)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5767,7 +5770,7 @@
       </c>
       <c r="I28" s="33" t="n">
         <f aca="false">G28/$G$5-1</f>
-        <v>0.404689092762487</v>
+        <v>0.496199782844734</v>
       </c>
       <c r="J28" s="34" t="n">
         <f aca="false">E28/G28</f>
@@ -5779,7 +5782,7 @@
       </c>
       <c r="L28" s="35" t="n">
         <f aca="false">RANK(H28,$H$5:$H$28)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5877,7 +5880,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
         <v>94</v>
       </c>
@@ -5888,36 +5891,36 @@
         <v>1312</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>882</v>
+        <v>1035</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>970</v>
+        <v>1152</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.9802</v>
+        <v>0.9862</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>1409</v>
+        <v>1383</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1626</v>
+        <v>1586</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1962</v>
+        <v>1842</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>0.9837</v>
+        <v>0.994</v>
       </c>
       <c r="L5" s="36" t="n">
         <f aca="false">IF(ISNUMBER(C5),F5/C5-1,"—")</f>
-        <v>0.00685975609756095</v>
+        <v>0.0114329268292683</v>
       </c>
       <c r="M5" s="25" t="n">
         <f aca="false">J5/F5-1</f>
-        <v>0.485238455715367</v>
+        <v>0.388093443858327</v>
       </c>
       <c r="N5" s="22" t="s">
         <v>223</v>
@@ -5926,7 +5929,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
         <v>96</v>
       </c>
@@ -5937,28 +5940,28 @@
         <v>226</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>1106</v>
+        <v>734</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1626</v>
+        <v>1384</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>1996</v>
+        <v>2259</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.9997</v>
+        <v>0.998</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>323</v>
+        <v>634</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>570</v>
+        <v>1216</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>1362</v>
+        <v>1883</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>0.9969</v>
+        <v>0.9968</v>
       </c>
       <c r="L6" s="37" t="str">
         <f aca="false">IF(ISNUMBER(C6),F6/C6-1,"—")</f>
@@ -5966,7 +5969,7 @@
       </c>
       <c r="M6" s="28" t="n">
         <f aca="false">J6/F6-1</f>
-        <v>-0.317635270541082</v>
+        <v>-0.166445329791943</v>
       </c>
       <c r="N6" s="24" t="s">
         <v>227</v>
@@ -5986,42 +5989,42 @@
         <v>2192</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2036</v>
+        <v>2017</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>2167</v>
+        <v>2186</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.9775</v>
+        <v>0.9886</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>1324</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2887</v>
+        <v>3504</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>0.9867</v>
+        <v>0.9942</v>
       </c>
       <c r="L7" s="36" t="n">
         <f aca="false">IF(ISNUMBER(C7),F7/C7-1,"—")</f>
-        <v>-0.011405109489051</v>
+        <v>-0.00273722627737227</v>
       </c>
       <c r="M7" s="25" t="n">
         <f aca="false">J7/F7-1</f>
-        <v>0.332256575911398</v>
+        <v>0.602927721866423</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6067,10 +6070,10 @@
         <v>0.81447963800905</v>
       </c>
       <c r="N8" s="23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6116,10 +6119,10 @@
         <v>0.90495867768595</v>
       </c>
       <c r="N9" s="22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6165,20 +6168,20 @@
         <v>0.934455270150576</v>
       </c>
       <c r="N10" s="23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -6212,26 +6215,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>90</v>
@@ -6246,16 +6249,16 @@
         <v>93</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6263,7 +6266,7 @@
         <v>182</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>5</v>
@@ -6284,13 +6287,13 @@
         <v>0.9974</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L5" s="25" t="n">
         <f aca="false">G5/$G$5-1</f>
@@ -6302,7 +6305,7 @@
         <v>184</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C6" s="30" t="n">
         <v>5</v>
@@ -6344,7 +6347,7 @@
         <v>101</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>5</v>
@@ -6386,7 +6389,7 @@
         <v>186</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C8" s="30" t="n">
         <v>15</v>
@@ -6428,7 +6431,7 @@
         <v>188</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>15</v>
@@ -6470,7 +6473,7 @@
         <v>190</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C10" s="30" t="n">
         <v>5</v>
@@ -6512,7 +6515,7 @@
         <v>192</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>10</v>
@@ -6554,7 +6557,7 @@
         <v>194</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C12" s="30" t="n">
         <v>5</v>
@@ -6596,7 +6599,7 @@
         <v>103</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C13" s="27" t="n">
         <v>5</v>
@@ -6635,10 +6638,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C14" s="30" t="n">
         <v>5</v>
@@ -6677,10 +6680,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>252</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>251</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>5</v>
@@ -6722,7 +6725,7 @@
         <v>104</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C16" s="30" t="n">
         <v>5</v>
@@ -6764,7 +6767,7 @@
         <v>198</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C17" s="27" t="n">
         <v>10</v>
@@ -6806,7 +6809,7 @@
         <v>200</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C18" s="30" t="n">
         <v>5</v>
@@ -6848,7 +6851,7 @@
         <v>202</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C19" s="35" t="n">
         <v>5</v>
@@ -6887,16 +6890,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C20" s="35" t="n">
         <v>5</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>1471</v>
@@ -6932,7 +6935,7 @@
         <v>105</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C21" s="35" t="n">
         <v>5</v>
@@ -6971,16 +6974,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C22" s="35" t="n">
         <v>5</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E22" s="15" t="n">
         <v>1716</v>
@@ -7013,17 +7016,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="43" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B27" s="44" t="s">
         <v>90</v>
@@ -7373,12 +7376,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7386,37 +7389,37 @@
         <v>88</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7462,7 +7465,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>1551</v>
@@ -7503,7 +7506,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>1551</v>
@@ -7544,7 +7547,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>2621</v>
@@ -7585,7 +7588,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>2621</v>
@@ -7626,7 +7629,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -7660,25 +7663,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>90</v>
@@ -7693,21 +7696,21 @@
         <v>93</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>2621</v>
@@ -7735,10 +7738,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>2621</v>
@@ -7766,10 +7769,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>2585</v>
@@ -7797,10 +7800,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>2621</v>
@@ -7828,10 +7831,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>1821</v>
@@ -7859,10 +7862,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>2171</v>
@@ -7890,10 +7893,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>1730</v>
@@ -7921,15 +7924,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>90</v>
@@ -7944,24 +7947,24 @@
         <v>93</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>2621</v>
@@ -7990,10 +7993,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>2566</v>
@@ -8022,10 +8025,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C19" s="15" t="n">
         <v>2621</v>
@@ -8054,10 +8057,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>1471</v>
@@ -8086,10 +8089,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>1696</v>
@@ -8118,10 +8121,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>1716</v>
@@ -8150,7 +8153,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8158,27 +8161,27 @@
         <v>88</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>1688</v>
@@ -8195,10 +8198,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>2618</v>
@@ -8215,10 +8218,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>1152</v>
@@ -8235,10 +8238,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C30" s="15" t="n">
         <v>1487</v>
@@ -8255,12 +8258,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/thesis-final/arabic/WSN_Protocol_Comparison_AR.xlsx
+++ b/thesis-final/arabic/WSN_Protocol_Comparison_AR.xlsx
@@ -350,7 +350,7 @@
     <t xml:space="preserve">أهم الأرقام</t>
   </si>
   <si>
-    <t xml:space="preserve">FND بتاع v8-Chain مقارنة بأحسن هجين من الأبحاث (H-LEACH المحسّن)</t>
+    <t xml:space="preserve">FND بتاع v8-Chain مقارنة بأحسن هجين من الأبحاث (SH-LEACH المحسّن)</t>
   </si>
   <si>
     <t xml:space="preserve">FND بتاع v8-Chain مقارنة بـ LEACH</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">FND بتاع v8-Chain لما الـ BS بعيد مقارنة بـ v7 بعيد</t>
   </si>
   <si>
-    <t xml:space="preserve">ملاحظة مهمة: LEACH وPEGASIS وHEED وSH-LEACH المحسّن عندهم PDR أعلى شوية من v8-Chain (99.40–99.79%)، بس أول نود فيهم بتموت قبلنا بـ 1,200 لـ 2,000 round. وPEGASIS عنده LND أعلى (3504)، بس أول نود فيه بتموت قبلنا بحوالي 1300 round.</t>
+    <t xml:space="preserve">ملاحظة مهمة: LEACH وPEGASIS وHEED وH-LEACH المحسّن عندهم PDR أعلى شوية من v8-Chain (99.36–99.68%)، بس أول نود فيهم بتموت قبلنا بـ 1,100 لـ 2,000 round. وPEGASIS عنده LND أعلى (3504)، بس أول نود فيه بتموت قبلنا بحوالي 1300 round.</t>
   </si>
   <si>
     <t xml:space="preserve">شرح المصطلحات بالعربي البسيط</t>
@@ -551,16 +551,16 @@
     <t xml:space="preserve">هجين من الأبحاث</t>
   </si>
   <si>
-    <t xml:space="preserve">LEACH + HEED بمضاعفة واحدة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مضاعفة متكررة حقيقية، Cprob من 0.10 لـ 0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شرط الطاقة = 1.0 × المتوسط</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شرط الطاقة اتخفف لـ 0.8 × المتوسط</t>
+    <t xml:space="preserve">معادلة 3 بالحرف: معامل الـ round بيكبر على طول (حوالي 29 CH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">معامل الـ round بقى بيلف كل 1/Cprob round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شرط الطاقة (أكبر من المتوسط) + عتبة LEACH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شرط ≥ + مجموعة G بتاعة LEACH (مرة كل 10 rounds)</t>
   </si>
   <si>
     <t xml:space="preserve">للمقارنة بس</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">EECH-HEED</t>
   </si>
   <si>
-    <t xml:space="preserve">HEED + EECH (مش LEACH+HEED)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ إرسال بس لما القراءة تتغير (بيبعت أقل)</t>
+    <t xml:space="preserve">منطقة HEED + منطقة EECH، عتبة معادلة 6، من غير sensing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التناوب في المنطقة 2 على نسبة الـ 10% بتاعة البحث</t>
   </si>
   <si>
     <t xml:space="preserve">v1</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">Lindsey و Raghavendra، 2002 — جدول 1 (50×50 م)</t>
   </si>
   <si>
-    <t xml:space="preserve">100 نود، Cprob = 0.10</t>
+    <t xml:space="preserve">100 نود، Cprob = 0.10، معادلة 3 بالحرف (حوالي 29 CH في الـ round)، معادلة راديو واحدة</t>
   </si>
   <si>
     <t xml:space="preserve">Shrestha وآخرين، 2015 — رسم بياني بس (Fig. 2)</t>
   </si>
   <si>
-    <t xml:space="preserve">مع حل احتياطي (الشرط الأصلي بيقف ومايختارش CH)</t>
+    <t xml:space="preserve">Algorithm 1، المتوسط على كل النودز؛ احتاج حل احتياطي في 132 round</t>
   </si>
   <si>
     <t xml:space="preserve">Razaque وآخرين، 2016 — مقروءة تقريبًا من Fig. 2</t>
   </si>
   <si>
-    <t xml:space="preserve">رسالة 4000 بت</t>
+    <t xml:space="preserve">سيناريو البحث: منطقتين 30/70، 56 جول، 4000 بت، والـ sensing (معادلة 7) شغّال</t>
   </si>
   <si>
     <t xml:space="preserve">Kaur و Kour و Singh، 2025 — جدول 7</t>
@@ -1595,10 +1595,10 @@
                   <c:v>1324</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1247</c:v>
+                  <c:v>1480</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2347</c:v>
+                  <c:v>1473</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1730</c:v>
@@ -1717,10 +1717,10 @@
                   <c:v>2352</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1600</c:v>
+                  <c:v>1542</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2449</c:v>
+                  <c:v>1509</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2081</c:v>
@@ -1839,10 +1839,10 @@
                   <c:v>3504</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1649</c:v>
+                  <c:v>1558</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2499</c:v>
+                  <c:v>1525</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2703</c:v>
@@ -1862,11 +1862,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="96485175"/>
-        <c:axId val="28098681"/>
+        <c:axId val="94305044"/>
+        <c:axId val="65432347"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="96485175"/>
+        <c:axId val="94305044"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1898,7 +1898,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28098681"/>
+        <c:crossAx val="65432347"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1906,7 +1906,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28098681"/>
+        <c:axId val="65432347"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1948,7 +1948,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96485175"/>
+        <c:crossAx val="94305044"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2149,10 +2149,10 @@
                   <c:v>0.9942</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9979</c:v>
+                  <c:v>0.9921</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9733</c:v>
+                  <c:v>0.9936</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.9772</c:v>
@@ -2172,11 +2172,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="93267099"/>
-        <c:axId val="22553498"/>
+        <c:axId val="87316220"/>
+        <c:axId val="89010729"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="93267099"/>
+        <c:axId val="87316220"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2208,7 +2208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22553498"/>
+        <c:crossAx val="89010729"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2216,7 +2216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22553498"/>
+        <c:axId val="89010729"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2260,7 +2260,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93267099"/>
+        <c:crossAx val="87316220"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2808,11 +2808,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96224763"/>
-        <c:axId val="67249896"/>
+        <c:axId val="71417707"/>
+        <c:axId val="31527422"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="96224763"/>
+        <c:axId val="71417707"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2844,7 +2844,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67249896"/>
+        <c:crossAx val="31527422"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2852,7 +2852,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67249896"/>
+        <c:axId val="31527422"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2928,7 +2928,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96224763"/>
+        <c:crossAx val="71417707"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3321,11 +3321,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="75480169"/>
-        <c:axId val="23161357"/>
+        <c:axId val="75018030"/>
+        <c:axId val="32465438"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="75480169"/>
+        <c:axId val="75018030"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3357,7 +3357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23161357"/>
+        <c:crossAx val="32465438"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3365,7 +3365,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23161357"/>
+        <c:axId val="32465438"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3441,7 +3441,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75480169"/>
+        <c:crossAx val="75018030"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4309,19 +4309,19 @@
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A8)*('المقارنة الموحدة'!$C$5:$C$28=B8),0),0))</f>
-        <v>1247</v>
+        <v>1480</v>
       </c>
       <c r="D8" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$F$5:$F$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A8)*('المقارنة الموحدة'!$C$5:$C$28=B8),0),0))</f>
-        <v>1600</v>
+        <v>1542</v>
       </c>
       <c r="E8" s="12" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$G$5:$G$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A8)*('المقارنة الموحدة'!$C$5:$C$28=B8),0),0))</f>
-        <v>1649</v>
+        <v>1558</v>
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$H$5:$H$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A8)*('المقارنة الموحدة'!$C$5:$C$28=B8),0),0))</f>
-        <v>0.9979</v>
+        <v>0.9921</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4333,19 +4333,19 @@
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$E$5:$E$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A9)*('المقارنة الموحدة'!$C$5:$C$28=B9),0),0))</f>
-        <v>2347</v>
+        <v>1473</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$F$5:$F$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A9)*('المقارنة الموحدة'!$C$5:$C$28=B9),0),0))</f>
-        <v>2449</v>
+        <v>1509</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$G$5:$G$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A9)*('المقارنة الموحدة'!$C$5:$C$28=B9),0),0))</f>
-        <v>2499</v>
+        <v>1525</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">INDEX('المقارنة الموحدة'!$H$5:$H$28,MATCH(1,INDEX(('المقارنة الموحدة'!$B$5:$B$28=A9)*('المقارنة الموحدة'!$C$5:$C$28=B9),0),0))</f>
-        <v>0.9733</v>
+        <v>0.9936</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4454,8 +4454,8 @@
         <v>107</v>
       </c>
       <c r="C16" s="19" t="n">
-        <f aca="false">C13/C9-1</f>
-        <v>0.116744780570942</v>
+        <f aca="false">C13/C8-1</f>
+        <v>0.770945945945946</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4812,11 +4812,11 @@
       </c>
       <c r="K5" s="27" t="n">
         <f aca="false">RANK(G5,$G$5:$G$28)</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L5" s="27" t="n">
         <f aca="false">RANK(H5,$H$5:$H$28)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="K6" s="30" t="n">
         <f aca="false">RANK(G6,$G$5:$G$28)</f>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L6" s="30" t="n">
         <f aca="false">RANK(H6,$H$5:$H$28)</f>
@@ -4896,11 +4896,11 @@
       </c>
       <c r="K7" s="27" t="n">
         <f aca="false">RANK(G7,$G$5:$G$28)</f>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L7" s="27" t="n">
         <f aca="false">RANK(H7,$H$5:$H$28)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4938,11 +4938,11 @@
       </c>
       <c r="K8" s="30" t="n">
         <f aca="false">RANK(G8,$G$5:$G$28)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="30" t="n">
         <f aca="false">RANK(H8,$H$5:$H$28)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4955,36 +4955,36 @@
       <c r="C9" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="22" t="s">
         <v>174</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>1440</v>
+        <v>647</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1584</v>
+        <v>702</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>1604</v>
+        <v>721</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.9917</v>
+        <v>0.9858</v>
       </c>
       <c r="I9" s="25" t="n">
         <f aca="false">G9/$G$5-1</f>
-        <v>-0.129207383279044</v>
+        <v>-0.608577633007601</v>
       </c>
       <c r="J9" s="26" t="n">
         <f aca="false">E9/G9</f>
-        <v>0.897755610972569</v>
+        <v>0.897364771151179</v>
       </c>
       <c r="K9" s="27" t="n">
         <f aca="false">RANK(G9,$G$5:$G$28)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L9" s="27" t="n">
         <f aca="false">RANK(H9,$H$5:$H$28)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5001,32 +5001,32 @@
         <v>175</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1247</v>
+        <v>1480</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1600</v>
+        <v>1542</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1649</v>
+        <v>1558</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.9979</v>
+        <v>0.9921</v>
       </c>
       <c r="I10" s="28" t="n">
         <f aca="false">G10/$G$5-1</f>
-        <v>-0.104777415852334</v>
+        <v>-0.154180238870793</v>
       </c>
       <c r="J10" s="29" t="n">
         <f aca="false">E10/G10</f>
-        <v>0.756215888417223</v>
+        <v>0.949935815147625</v>
       </c>
       <c r="K10" s="30" t="n">
         <f aca="false">RANK(G10,$G$5:$G$28)</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L10" s="30" t="n">
         <f aca="false">RANK(H10,$H$5:$H$28)</f>
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5039,36 +5039,36 @@
       <c r="C11" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="22" t="s">
         <v>176</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2177</v>
+        <v>1384</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2255</v>
+        <v>1419</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>2305</v>
+        <v>1434</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.9733</v>
+        <v>0.993</v>
       </c>
       <c r="I11" s="25" t="n">
         <f aca="false">G11/$G$5-1</f>
-        <v>0.251357220412595</v>
+        <v>-0.221498371335505</v>
       </c>
       <c r="J11" s="26" t="n">
         <f aca="false">E11/G11</f>
-        <v>0.944468546637744</v>
+        <v>0.96513249651325</v>
       </c>
       <c r="K11" s="27" t="n">
         <f aca="false">RANK(G11,$G$5:$G$28)</f>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L11" s="27" t="n">
         <f aca="false">RANK(H11,$H$5:$H$28)</f>
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5085,32 +5085,32 @@
         <v>177</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>2347</v>
+        <v>1473</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>2449</v>
+        <v>1509</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>2499</v>
+        <v>1525</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.9733</v>
+        <v>0.9936</v>
       </c>
       <c r="I12" s="28" t="n">
         <f aca="false">G12/$G$5-1</f>
-        <v>0.356677524429967</v>
+        <v>-0.172095548317047</v>
       </c>
       <c r="J12" s="29" t="n">
         <f aca="false">E12/G12</f>
-        <v>0.939175670268107</v>
+        <v>0.965901639344262</v>
       </c>
       <c r="K12" s="30" t="n">
         <f aca="false">RANK(G12,$G$5:$G$28)</f>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L12" s="30" t="n">
         <f aca="false">RANK(H12,$H$5:$H$28)</f>
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5127,32 +5127,32 @@
         <v>180</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>1653</v>
+        <v>1311</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2134</v>
+        <v>1382</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>2184</v>
+        <v>1545</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.9168</v>
+        <v>0.9974</v>
       </c>
       <c r="I13" s="25" t="n">
         <f aca="false">G13/$G$5-1</f>
-        <v>0.185667752442997</v>
+        <v>-0.161237785016287</v>
       </c>
       <c r="J13" s="26" t="n">
         <f aca="false">E13/G13</f>
-        <v>0.756868131868132</v>
+        <v>0.848543689320388</v>
       </c>
       <c r="K13" s="27" t="n">
         <f aca="false">RANK(G13,$G$5:$G$28)</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L13" s="27" t="n">
         <f aca="false">RANK(H13,$H$5:$H$28)</f>
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5169,32 +5169,32 @@
         <v>181</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2502</v>
+        <v>1368</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>3758</v>
+        <v>1385</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>3808</v>
+        <v>1767</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.9214</v>
+        <v>0.9951</v>
       </c>
       <c r="I14" s="28" t="n">
         <f aca="false">G14/$G$5-1</f>
-        <v>1.06731813246471</v>
+        <v>-0.0407166123778502</v>
       </c>
       <c r="J14" s="29" t="n">
         <f aca="false">E14/G14</f>
-        <v>0.65703781512605</v>
+        <v>0.774193548387097</v>
       </c>
       <c r="K14" s="30" t="n">
         <f aca="false">RANK(G14,$G$5:$G$28)</f>
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L14" s="30" t="n">
         <f aca="false">RANK(H14,$H$5:$H$28)</f>
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5232,11 +5232,11 @@
       </c>
       <c r="K15" s="27" t="n">
         <f aca="false">RANK(G15,$G$5:$G$28)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" s="27" t="n">
         <f aca="false">RANK(H15,$H$5:$H$28)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="K16" s="30" t="n">
         <f aca="false">RANK(G16,$G$5:$G$28)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L16" s="30" t="n">
         <f aca="false">RANK(H16,$H$5:$H$28)</f>
@@ -5316,11 +5316,11 @@
       </c>
       <c r="K17" s="27" t="n">
         <f aca="false">RANK(G17,$G$5:$G$28)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L17" s="27" t="n">
         <f aca="false">RANK(H17,$H$5:$H$28)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5358,11 +5358,11 @@
       </c>
       <c r="K18" s="30" t="n">
         <f aca="false">RANK(G18,$G$5:$G$28)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L18" s="30" t="n">
         <f aca="false">RANK(H18,$H$5:$H$28)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5400,11 +5400,11 @@
       </c>
       <c r="K19" s="27" t="n">
         <f aca="false">RANK(G19,$G$5:$G$28)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L19" s="27" t="n">
         <f aca="false">RANK(H19,$H$5:$H$28)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5442,11 +5442,11 @@
       </c>
       <c r="K20" s="30" t="n">
         <f aca="false">RANK(G20,$G$5:$G$28)</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L20" s="30" t="n">
         <f aca="false">RANK(H20,$H$5:$H$28)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5484,11 +5484,11 @@
       </c>
       <c r="K21" s="27" t="n">
         <f aca="false">RANK(G21,$G$5:$G$28)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L21" s="27" t="n">
         <f aca="false">RANK(H21,$H$5:$H$28)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5526,11 +5526,11 @@
       </c>
       <c r="K22" s="30" t="n">
         <f aca="false">RANK(G22,$G$5:$G$28)</f>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L22" s="30" t="n">
         <f aca="false">RANK(H22,$H$5:$H$28)</f>
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="K23" s="27" t="n">
         <f aca="false">RANK(G23,$G$5:$G$28)</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L23" s="27" t="n">
         <f aca="false">RANK(H23,$H$5:$H$28)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5610,11 +5610,11 @@
       </c>
       <c r="K24" s="30" t="n">
         <f aca="false">RANK(G24,$G$5:$G$28)</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L24" s="30" t="n">
         <f aca="false">RANK(H24,$H$5:$H$28)</f>
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5652,11 +5652,11 @@
       </c>
       <c r="K25" s="27" t="n">
         <f aca="false">RANK(G25,$G$5:$G$28)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L25" s="27" t="n">
         <f aca="false">RANK(H25,$H$5:$H$28)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5694,11 +5694,11 @@
       </c>
       <c r="K26" s="30" t="n">
         <f aca="false">RANK(G26,$G$5:$G$28)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" s="30" t="n">
         <f aca="false">RANK(H26,$H$5:$H$28)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5736,11 +5736,11 @@
       </c>
       <c r="K27" s="35" t="n">
         <f aca="false">RANK(G27,$G$5:$G$28)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L27" s="35" t="n">
         <f aca="false">RANK(H27,$H$5:$H$28)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5778,11 +5778,11 @@
       </c>
       <c r="K28" s="35" t="n">
         <f aca="false">RANK(G28,$G$5:$G$28)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L28" s="35" t="n">
         <f aca="false">RANK(H28,$H$5:$H$28)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6027,7 +6027,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
         <v>98</v>
       </c>
@@ -6038,28 +6038,28 @@
         <v>226</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>747</v>
+        <v>583</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>884</v>
+        <v>689</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.9953</v>
+        <v>0.9966</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1440</v>
+        <v>647</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>1584</v>
+        <v>702</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>1604</v>
+        <v>721</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0.9917</v>
+        <v>0.9858</v>
       </c>
       <c r="L8" s="37" t="str">
         <f aca="false">IF(ISNUMBER(C8),F8/C8-1,"—")</f>
@@ -6067,16 +6067,16 @@
       </c>
       <c r="M8" s="28" t="n">
         <f aca="false">J8/F8-1</f>
-        <v>0.81447963800905</v>
-      </c>
-      <c r="N8" s="23" t="s">
+        <v>0.04644412191582</v>
+      </c>
+      <c r="N8" s="24" t="s">
         <v>231</v>
       </c>
       <c r="O8" s="24" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
         <v>100</v>
       </c>
@@ -6087,36 +6087,36 @@
         <v>4312</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.9475</v>
+        <v>0.9504</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2177</v>
+        <v>1384</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>2255</v>
+        <v>1419</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2305</v>
+        <v>1434</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>0.9733</v>
+        <v>0.993</v>
       </c>
       <c r="L9" s="36" t="n">
         <f aca="false">IF(ISNUMBER(C9),F9/C9-1,"—")</f>
-        <v>-0.719387755102041</v>
+        <v>-0.720083487940631</v>
       </c>
       <c r="M9" s="25" t="n">
         <f aca="false">J9/F9-1</f>
-        <v>0.90495867768595</v>
+        <v>0.188069594034797</v>
       </c>
       <c r="N9" s="22" t="s">
         <v>233</v>
@@ -6125,7 +6125,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
         <v>179</v>
       </c>
@@ -6136,38 +6136,38 @@
         <v>2200</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>792</v>
+        <v>1121</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1079</v>
+        <v>1954</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1129</v>
+        <v>3783</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.9043</v>
+        <v>0.9978</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1653</v>
+        <v>1311</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>2134</v>
+        <v>1382</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>2184</v>
+        <v>1545</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>0.9168</v>
+        <v>0.9974</v>
       </c>
       <c r="L10" s="37" t="n">
         <f aca="false">IF(ISNUMBER(C10),F10/C10-1,"—")</f>
-        <v>-0.486818181818182</v>
+        <v>0.719545454545455</v>
       </c>
       <c r="M10" s="28" t="n">
         <f aca="false">J10/F10-1</f>
-        <v>0.934455270150576</v>
-      </c>
-      <c r="N10" s="23" t="s">
+        <v>-0.591593973037272</v>
+      </c>
+      <c r="N10" s="24" t="s">
         <v>235</v>
       </c>
       <c r="O10" s="24" t="s">
